--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3600"/>
+  <dimension ref="A1:C3673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51511,6 +51511,809 @@
         <v>436</v>
       </c>
     </row>
+    <row r="3601">
+      <c r="A3601" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3601" t="inlineStr"/>
+      <c r="C3601" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3602">
+      <c r="A3602" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3602" t="inlineStr"/>
+      <c r="C3602" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3603">
+      <c r="A3603" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3603" t="inlineStr"/>
+      <c r="C3603" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3604">
+      <c r="A3604" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3604" t="inlineStr"/>
+      <c r="C3604" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3605">
+      <c r="A3605" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3605" t="inlineStr"/>
+      <c r="C3605" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3606">
+      <c r="A3606" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3606" t="inlineStr"/>
+      <c r="C3606" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3607">
+      <c r="A3607" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3607" t="inlineStr"/>
+      <c r="C3607" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3608">
+      <c r="A3608" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3608" t="inlineStr"/>
+      <c r="C3608" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3609">
+      <c r="A3609" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3609" t="inlineStr"/>
+      <c r="C3609" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3610">
+      <c r="A3610" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3610" t="inlineStr"/>
+      <c r="C3610" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3611">
+      <c r="A3611" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3611" t="inlineStr"/>
+      <c r="C3611" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3612">
+      <c r="A3612" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3612" t="inlineStr"/>
+      <c r="C3612" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3613">
+      <c r="A3613" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3613" t="inlineStr"/>
+      <c r="C3613" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3614">
+      <c r="A3614" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3614" t="inlineStr"/>
+      <c r="C3614" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3615">
+      <c r="A3615" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3615" t="inlineStr"/>
+      <c r="C3615" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3616">
+      <c r="A3616" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3616" t="inlineStr"/>
+      <c r="C3616" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3617">
+      <c r="A3617" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3617" t="inlineStr"/>
+      <c r="C3617" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3618">
+      <c r="A3618" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3618" t="inlineStr"/>
+      <c r="C3618" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3619">
+      <c r="A3619" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3619" t="inlineStr"/>
+      <c r="C3619" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3620">
+      <c r="A3620" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3620" t="inlineStr"/>
+      <c r="C3620" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3621">
+      <c r="A3621" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3621" t="inlineStr"/>
+      <c r="C3621" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3622">
+      <c r="A3622" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3622" t="inlineStr"/>
+      <c r="C3622" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3623">
+      <c r="A3623" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3623" t="inlineStr"/>
+      <c r="C3623" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3624">
+      <c r="A3624" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3624" t="inlineStr"/>
+      <c r="C3624" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3625">
+      <c r="A3625" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3625" t="inlineStr"/>
+      <c r="C3625" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3626">
+      <c r="A3626" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3626" t="inlineStr"/>
+      <c r="C3626" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3627">
+      <c r="A3627" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3627" t="inlineStr"/>
+      <c r="C3627" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3628">
+      <c r="A3628" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3628" t="inlineStr"/>
+      <c r="C3628" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3629">
+      <c r="A3629" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3629" t="inlineStr"/>
+      <c r="C3629" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3630">
+      <c r="A3630" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3630" t="inlineStr"/>
+      <c r="C3630" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3631">
+      <c r="A3631" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3631" t="inlineStr"/>
+      <c r="C3631" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3632">
+      <c r="A3632" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3632" t="inlineStr"/>
+      <c r="C3632" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3633">
+      <c r="A3633" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3633" t="inlineStr"/>
+      <c r="C3633" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3634">
+      <c r="A3634" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3634" t="inlineStr"/>
+      <c r="C3634" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3635">
+      <c r="A3635" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3635" t="inlineStr"/>
+      <c r="C3635" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3636">
+      <c r="A3636" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3636" t="inlineStr"/>
+      <c r="C3636" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3637">
+      <c r="A3637" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3637" t="inlineStr"/>
+      <c r="C3637" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3638">
+      <c r="A3638" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3638" t="inlineStr"/>
+      <c r="C3638" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3639">
+      <c r="A3639" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3639" t="inlineStr"/>
+      <c r="C3639" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3640">
+      <c r="A3640" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3640" t="inlineStr"/>
+      <c r="C3640" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3641">
+      <c r="A3641" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3641" t="inlineStr"/>
+      <c r="C3641" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3642">
+      <c r="A3642" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3642" t="inlineStr"/>
+      <c r="C3642" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3643">
+      <c r="A3643" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3643" t="inlineStr"/>
+      <c r="C3643" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3644">
+      <c r="A3644" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3644" t="inlineStr"/>
+      <c r="C3644" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3645">
+      <c r="A3645" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3645" t="inlineStr"/>
+      <c r="C3645" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3646">
+      <c r="A3646" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3646" t="inlineStr"/>
+      <c r="C3646" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3647">
+      <c r="A3647" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3647" t="inlineStr"/>
+      <c r="C3647" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3648">
+      <c r="A3648" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3648" t="inlineStr"/>
+      <c r="C3648" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3649">
+      <c r="A3649" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3649" t="inlineStr"/>
+      <c r="C3649" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3650">
+      <c r="A3650" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3650" t="inlineStr"/>
+      <c r="C3650" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3651">
+      <c r="A3651" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3651" t="inlineStr"/>
+      <c r="C3651" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3652">
+      <c r="A3652" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3652" t="inlineStr"/>
+      <c r="C3652" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3653">
+      <c r="A3653" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3653" t="inlineStr"/>
+      <c r="C3653" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3654">
+      <c r="A3654" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3654" t="inlineStr"/>
+      <c r="C3654" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3655">
+      <c r="A3655" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3655" t="inlineStr"/>
+      <c r="C3655" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3656">
+      <c r="A3656" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3656" t="inlineStr"/>
+      <c r="C3656" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3657">
+      <c r="A3657" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3657" t="inlineStr"/>
+      <c r="C3657" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3658">
+      <c r="A3658" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3658" t="inlineStr"/>
+      <c r="C3658" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3659">
+      <c r="A3659" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3659" t="inlineStr"/>
+      <c r="C3659" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3660">
+      <c r="A3660" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3660" t="inlineStr"/>
+      <c r="C3660" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3661">
+      <c r="A3661" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3661" t="inlineStr"/>
+      <c r="C3661" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3662">
+      <c r="A3662" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3662" t="inlineStr"/>
+      <c r="C3662" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3663">
+      <c r="A3663" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3663" t="inlineStr"/>
+      <c r="C3663" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3664">
+      <c r="A3664" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3664" t="inlineStr"/>
+      <c r="C3664" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3665">
+      <c r="A3665" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3665" t="inlineStr"/>
+      <c r="C3665" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3666">
+      <c r="A3666" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3666" t="inlineStr"/>
+      <c r="C3666" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3667">
+      <c r="A3667" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3667" t="inlineStr"/>
+      <c r="C3667" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3668">
+      <c r="A3668" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3668" t="inlineStr"/>
+      <c r="C3668" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3669">
+      <c r="A3669" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3669" t="inlineStr"/>
+      <c r="C3669" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3670">
+      <c r="A3670" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3670" t="inlineStr"/>
+      <c r="C3670" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3671">
+      <c r="A3671" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3671" t="inlineStr"/>
+      <c r="C3671" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3672">
+      <c r="A3672" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3672" t="inlineStr"/>
+      <c r="C3672" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="3673">
+      <c r="A3673" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3673" t="inlineStr"/>
+      <c r="C3673" t="n">
+        <v>437</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3673"/>
+  <dimension ref="A1:C4258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52314,6 +52314,6446 @@
         <v>437</v>
       </c>
     </row>
+    <row r="3674">
+      <c r="A3674" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3674" t="inlineStr"/>
+      <c r="C3674" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3675">
+      <c r="A3675" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3675" t="inlineStr"/>
+      <c r="C3675" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3676">
+      <c r="A3676" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3676" t="inlineStr"/>
+      <c r="C3676" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3677">
+      <c r="A3677" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3677" t="inlineStr"/>
+      <c r="C3677" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3678">
+      <c r="A3678" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3678" t="inlineStr"/>
+      <c r="C3678" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3679">
+      <c r="A3679" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3679" t="inlineStr"/>
+      <c r="C3679" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3680">
+      <c r="A3680" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3680" t="inlineStr"/>
+      <c r="C3680" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3681">
+      <c r="A3681" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3681" t="inlineStr"/>
+      <c r="C3681" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3682">
+      <c r="A3682" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3682" t="inlineStr"/>
+      <c r="C3682" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3683">
+      <c r="A3683" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3683" t="inlineStr"/>
+      <c r="C3683" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3684">
+      <c r="A3684" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3684" t="inlineStr"/>
+      <c r="C3684" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3685">
+      <c r="A3685" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3685" t="inlineStr"/>
+      <c r="C3685" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3686">
+      <c r="A3686" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3686" t="inlineStr"/>
+      <c r="C3686" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3687">
+      <c r="A3687" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3687" t="inlineStr"/>
+      <c r="C3687" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3688">
+      <c r="A3688" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3688" t="inlineStr"/>
+      <c r="C3688" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3689">
+      <c r="A3689" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3689" t="inlineStr"/>
+      <c r="C3689" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3690">
+      <c r="A3690" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3690" t="inlineStr"/>
+      <c r="C3690" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3691">
+      <c r="A3691" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3691" t="inlineStr"/>
+      <c r="C3691" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3692">
+      <c r="A3692" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3692" t="inlineStr"/>
+      <c r="C3692" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3693">
+      <c r="A3693" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3693" t="inlineStr"/>
+      <c r="C3693" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3694">
+      <c r="A3694" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3694" t="inlineStr"/>
+      <c r="C3694" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3695">
+      <c r="A3695" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3695" t="inlineStr"/>
+      <c r="C3695" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3696">
+      <c r="A3696" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3696" t="inlineStr"/>
+      <c r="C3696" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3697">
+      <c r="A3697" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3697" t="inlineStr"/>
+      <c r="C3697" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3698">
+      <c r="A3698" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3698" t="inlineStr"/>
+      <c r="C3698" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3699">
+      <c r="A3699" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3699" t="inlineStr"/>
+      <c r="C3699" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3700">
+      <c r="A3700" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3700" t="inlineStr"/>
+      <c r="C3700" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3701">
+      <c r="A3701" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3701" t="inlineStr"/>
+      <c r="C3701" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3702">
+      <c r="A3702" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3702" t="inlineStr"/>
+      <c r="C3702" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3703">
+      <c r="A3703" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3703" t="inlineStr"/>
+      <c r="C3703" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3704">
+      <c r="A3704" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3704" t="inlineStr"/>
+      <c r="C3704" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3705">
+      <c r="A3705" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3705" t="inlineStr"/>
+      <c r="C3705" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3706">
+      <c r="A3706" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3706" t="inlineStr"/>
+      <c r="C3706" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3707">
+      <c r="A3707" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3707" t="inlineStr"/>
+      <c r="C3707" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3708">
+      <c r="A3708" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3708" t="inlineStr"/>
+      <c r="C3708" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3709">
+      <c r="A3709" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3709" t="inlineStr"/>
+      <c r="C3709" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3710">
+      <c r="A3710" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3710" t="inlineStr"/>
+      <c r="C3710" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3711">
+      <c r="A3711" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3711" t="inlineStr"/>
+      <c r="C3711" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3712">
+      <c r="A3712" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3712" t="inlineStr"/>
+      <c r="C3712" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3713">
+      <c r="A3713" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3713" t="inlineStr"/>
+      <c r="C3713" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3714">
+      <c r="A3714" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3714" t="inlineStr"/>
+      <c r="C3714" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3715">
+      <c r="A3715" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3715" t="inlineStr"/>
+      <c r="C3715" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3716">
+      <c r="A3716" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3716" t="inlineStr"/>
+      <c r="C3716" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3717">
+      <c r="A3717" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3717" t="inlineStr"/>
+      <c r="C3717" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3718">
+      <c r="A3718" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3718" t="inlineStr"/>
+      <c r="C3718" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3719">
+      <c r="A3719" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3719" t="inlineStr"/>
+      <c r="C3719" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3720">
+      <c r="A3720" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3720" t="inlineStr"/>
+      <c r="C3720" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3721">
+      <c r="A3721" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3721" t="inlineStr"/>
+      <c r="C3721" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3722">
+      <c r="A3722" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3722" t="inlineStr"/>
+      <c r="C3722" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3723">
+      <c r="A3723" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3723" t="inlineStr"/>
+      <c r="C3723" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3724">
+      <c r="A3724" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3724" t="inlineStr"/>
+      <c r="C3724" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3725">
+      <c r="A3725" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3725" t="inlineStr"/>
+      <c r="C3725" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3726">
+      <c r="A3726" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3726" t="inlineStr"/>
+      <c r="C3726" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3727">
+      <c r="A3727" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3727" t="inlineStr"/>
+      <c r="C3727" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3728">
+      <c r="A3728" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3728" t="inlineStr"/>
+      <c r="C3728" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3729">
+      <c r="A3729" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3729" t="inlineStr"/>
+      <c r="C3729" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3730">
+      <c r="A3730" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3730" t="inlineStr"/>
+      <c r="C3730" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3731">
+      <c r="A3731" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3731" t="inlineStr"/>
+      <c r="C3731" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3732">
+      <c r="A3732" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3732" t="inlineStr"/>
+      <c r="C3732" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3733">
+      <c r="A3733" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3733" t="inlineStr"/>
+      <c r="C3733" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3734">
+      <c r="A3734" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3734" t="inlineStr"/>
+      <c r="C3734" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3735">
+      <c r="A3735" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3735" t="inlineStr"/>
+      <c r="C3735" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3736">
+      <c r="A3736" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3736" t="inlineStr"/>
+      <c r="C3736" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3737">
+      <c r="A3737" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3737" t="inlineStr"/>
+      <c r="C3737" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3738">
+      <c r="A3738" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3738" t="inlineStr"/>
+      <c r="C3738" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3739">
+      <c r="A3739" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3739" t="inlineStr"/>
+      <c r="C3739" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3740">
+      <c r="A3740" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3740" t="inlineStr"/>
+      <c r="C3740" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3741">
+      <c r="A3741" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3741" t="inlineStr"/>
+      <c r="C3741" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3742">
+      <c r="A3742" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3742" t="inlineStr"/>
+      <c r="C3742" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3743">
+      <c r="A3743" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3743" t="inlineStr"/>
+      <c r="C3743" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3744">
+      <c r="A3744" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3744" t="inlineStr"/>
+      <c r="C3744" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3745">
+      <c r="A3745" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3745" t="inlineStr"/>
+      <c r="C3745" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3746">
+      <c r="A3746" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3746" t="inlineStr"/>
+      <c r="C3746" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3747">
+      <c r="A3747" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3747" t="inlineStr"/>
+      <c r="C3747" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3748">
+      <c r="A3748" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3748" t="inlineStr"/>
+      <c r="C3748" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3749">
+      <c r="A3749" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3749" t="inlineStr"/>
+      <c r="C3749" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3750">
+      <c r="A3750" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3750" t="inlineStr"/>
+      <c r="C3750" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3751">
+      <c r="A3751" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3751" t="inlineStr"/>
+      <c r="C3751" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3752">
+      <c r="A3752" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3752" t="inlineStr"/>
+      <c r="C3752" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3753">
+      <c r="A3753" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3753" t="inlineStr"/>
+      <c r="C3753" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3754">
+      <c r="A3754" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3754" t="inlineStr"/>
+      <c r="C3754" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3755">
+      <c r="A3755" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3755" t="inlineStr"/>
+      <c r="C3755" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3756">
+      <c r="A3756" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3756" t="inlineStr"/>
+      <c r="C3756" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3757">
+      <c r="A3757" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3757" t="inlineStr"/>
+      <c r="C3757" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3758">
+      <c r="A3758" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3758" t="inlineStr"/>
+      <c r="C3758" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3759">
+      <c r="A3759" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3759" t="inlineStr"/>
+      <c r="C3759" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3760">
+      <c r="A3760" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3760" t="inlineStr"/>
+      <c r="C3760" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3761">
+      <c r="A3761" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3761" t="inlineStr"/>
+      <c r="C3761" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3762">
+      <c r="A3762" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3762" t="inlineStr"/>
+      <c r="C3762" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3763">
+      <c r="A3763" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3763" t="inlineStr"/>
+      <c r="C3763" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3764">
+      <c r="A3764" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3764" t="inlineStr"/>
+      <c r="C3764" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3765">
+      <c r="A3765" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3765" t="inlineStr"/>
+      <c r="C3765" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3766">
+      <c r="A3766" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3766" t="inlineStr"/>
+      <c r="C3766" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3767">
+      <c r="A3767" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3767" t="inlineStr"/>
+      <c r="C3767" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3768">
+      <c r="A3768" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3768" t="inlineStr"/>
+      <c r="C3768" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3769">
+      <c r="A3769" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3769" t="inlineStr"/>
+      <c r="C3769" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3770">
+      <c r="A3770" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3770" t="inlineStr"/>
+      <c r="C3770" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3771">
+      <c r="A3771" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3771" t="inlineStr"/>
+      <c r="C3771" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3772">
+      <c r="A3772" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3772" t="inlineStr"/>
+      <c r="C3772" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3773">
+      <c r="A3773" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3773" t="inlineStr"/>
+      <c r="C3773" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3774">
+      <c r="A3774" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3774" t="inlineStr"/>
+      <c r="C3774" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3775">
+      <c r="A3775" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3775" t="inlineStr"/>
+      <c r="C3775" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3776">
+      <c r="A3776" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3776" t="inlineStr"/>
+      <c r="C3776" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3777">
+      <c r="A3777" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3777" t="inlineStr"/>
+      <c r="C3777" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3778">
+      <c r="A3778" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3778" t="inlineStr"/>
+      <c r="C3778" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3779">
+      <c r="A3779" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3779" t="inlineStr"/>
+      <c r="C3779" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3780">
+      <c r="A3780" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3780" t="inlineStr"/>
+      <c r="C3780" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3781">
+      <c r="A3781" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3781" t="inlineStr"/>
+      <c r="C3781" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3782">
+      <c r="A3782" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3782" t="inlineStr"/>
+      <c r="C3782" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3783">
+      <c r="A3783" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3783" t="inlineStr"/>
+      <c r="C3783" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3784">
+      <c r="A3784" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3784" t="inlineStr"/>
+      <c r="C3784" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3785">
+      <c r="A3785" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3785" t="inlineStr"/>
+      <c r="C3785" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3786">
+      <c r="A3786" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3786" t="inlineStr"/>
+      <c r="C3786" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3787">
+      <c r="A3787" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3787" t="inlineStr"/>
+      <c r="C3787" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3788">
+      <c r="A3788" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3788" t="inlineStr"/>
+      <c r="C3788" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3789">
+      <c r="A3789" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3789" t="inlineStr"/>
+      <c r="C3789" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3790">
+      <c r="A3790" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3790" t="inlineStr"/>
+      <c r="C3790" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3791">
+      <c r="A3791" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3791" t="inlineStr"/>
+      <c r="C3791" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3792">
+      <c r="A3792" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3792" t="inlineStr"/>
+      <c r="C3792" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3793">
+      <c r="A3793" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3793" t="inlineStr"/>
+      <c r="C3793" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3794">
+      <c r="A3794" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3794" t="inlineStr"/>
+      <c r="C3794" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3795">
+      <c r="A3795" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3795" t="inlineStr"/>
+      <c r="C3795" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3796">
+      <c r="A3796" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3796" t="inlineStr"/>
+      <c r="C3796" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3797">
+      <c r="A3797" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3797" t="inlineStr"/>
+      <c r="C3797" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3798">
+      <c r="A3798" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3798" t="inlineStr"/>
+      <c r="C3798" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3799">
+      <c r="A3799" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3799" t="inlineStr"/>
+      <c r="C3799" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3800">
+      <c r="A3800" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3800" t="inlineStr"/>
+      <c r="C3800" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3801">
+      <c r="A3801" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3801" t="inlineStr"/>
+      <c r="C3801" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3802">
+      <c r="A3802" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3802" t="inlineStr"/>
+      <c r="C3802" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3803">
+      <c r="A3803" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3803" t="inlineStr"/>
+      <c r="C3803" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3804">
+      <c r="A3804" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3804" t="inlineStr"/>
+      <c r="C3804" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3805">
+      <c r="A3805" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3805" t="inlineStr"/>
+      <c r="C3805" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3806">
+      <c r="A3806" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3806" t="inlineStr"/>
+      <c r="C3806" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3807">
+      <c r="A3807" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3807" t="inlineStr"/>
+      <c r="C3807" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3808">
+      <c r="A3808" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3808" t="inlineStr"/>
+      <c r="C3808" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3809">
+      <c r="A3809" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3809" t="inlineStr"/>
+      <c r="C3809" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3810">
+      <c r="A3810" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3810" t="inlineStr"/>
+      <c r="C3810" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3811">
+      <c r="A3811" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3811" t="inlineStr"/>
+      <c r="C3811" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3812">
+      <c r="A3812" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3812" t="inlineStr"/>
+      <c r="C3812" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3813">
+      <c r="A3813" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3813" t="inlineStr"/>
+      <c r="C3813" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3814">
+      <c r="A3814" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3814" t="inlineStr"/>
+      <c r="C3814" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3815">
+      <c r="A3815" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3815" t="inlineStr"/>
+      <c r="C3815" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3816">
+      <c r="A3816" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3816" t="inlineStr"/>
+      <c r="C3816" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3817">
+      <c r="A3817" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3817" t="inlineStr"/>
+      <c r="C3817" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3818">
+      <c r="A3818" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3818" t="inlineStr"/>
+      <c r="C3818" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3819">
+      <c r="A3819" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3819" t="inlineStr"/>
+      <c r="C3819" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="3820">
+      <c r="A3820" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3820" t="inlineStr"/>
+      <c r="C3820" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3821">
+      <c r="A3821" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3821" t="inlineStr"/>
+      <c r="C3821" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3822">
+      <c r="A3822" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3822" t="inlineStr"/>
+      <c r="C3822" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3823">
+      <c r="A3823" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3823" t="inlineStr"/>
+      <c r="C3823" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3824">
+      <c r="A3824" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3824" t="inlineStr"/>
+      <c r="C3824" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3825">
+      <c r="A3825" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3825" t="inlineStr"/>
+      <c r="C3825" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3826">
+      <c r="A3826" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3826" t="inlineStr"/>
+      <c r="C3826" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3827">
+      <c r="A3827" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3827" t="inlineStr"/>
+      <c r="C3827" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3828">
+      <c r="A3828" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3828" t="inlineStr"/>
+      <c r="C3828" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3829">
+      <c r="A3829" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3829" t="inlineStr"/>
+      <c r="C3829" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3830">
+      <c r="A3830" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3830" t="inlineStr"/>
+      <c r="C3830" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3831">
+      <c r="A3831" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3831" t="inlineStr"/>
+      <c r="C3831" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3832">
+      <c r="A3832" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3832" t="inlineStr"/>
+      <c r="C3832" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3833">
+      <c r="A3833" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3833" t="inlineStr"/>
+      <c r="C3833" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3834">
+      <c r="A3834" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3834" t="inlineStr"/>
+      <c r="C3834" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3835">
+      <c r="A3835" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3835" t="inlineStr"/>
+      <c r="C3835" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3836">
+      <c r="A3836" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3836" t="inlineStr"/>
+      <c r="C3836" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3837">
+      <c r="A3837" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3837" t="inlineStr"/>
+      <c r="C3837" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3838">
+      <c r="A3838" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3838" t="inlineStr"/>
+      <c r="C3838" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3839">
+      <c r="A3839" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3839" t="inlineStr"/>
+      <c r="C3839" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3840">
+      <c r="A3840" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3840" t="inlineStr"/>
+      <c r="C3840" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3841">
+      <c r="A3841" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3841" t="inlineStr"/>
+      <c r="C3841" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3842">
+      <c r="A3842" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3842" t="inlineStr"/>
+      <c r="C3842" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3843">
+      <c r="A3843" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3843" t="inlineStr"/>
+      <c r="C3843" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3844">
+      <c r="A3844" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3844" t="inlineStr"/>
+      <c r="C3844" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3845">
+      <c r="A3845" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3845" t="inlineStr"/>
+      <c r="C3845" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3846">
+      <c r="A3846" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3846" t="inlineStr"/>
+      <c r="C3846" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3847">
+      <c r="A3847" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3847" t="inlineStr"/>
+      <c r="C3847" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3848">
+      <c r="A3848" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3848" t="inlineStr"/>
+      <c r="C3848" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3849">
+      <c r="A3849" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3849" t="inlineStr"/>
+      <c r="C3849" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3850">
+      <c r="A3850" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3850" t="inlineStr"/>
+      <c r="C3850" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3851">
+      <c r="A3851" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3851" t="inlineStr"/>
+      <c r="C3851" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3852">
+      <c r="A3852" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3852" t="inlineStr"/>
+      <c r="C3852" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3853">
+      <c r="A3853" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3853" t="inlineStr"/>
+      <c r="C3853" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3854">
+      <c r="A3854" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3854" t="inlineStr"/>
+      <c r="C3854" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3855">
+      <c r="A3855" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3855" t="inlineStr"/>
+      <c r="C3855" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3856">
+      <c r="A3856" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3856" t="inlineStr"/>
+      <c r="C3856" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3857">
+      <c r="A3857" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3857" t="inlineStr"/>
+      <c r="C3857" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3858">
+      <c r="A3858" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3858" t="inlineStr"/>
+      <c r="C3858" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3859">
+      <c r="A3859" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3859" t="inlineStr"/>
+      <c r="C3859" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3860">
+      <c r="A3860" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3860" t="inlineStr"/>
+      <c r="C3860" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3861">
+      <c r="A3861" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3861" t="inlineStr"/>
+      <c r="C3861" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3862">
+      <c r="A3862" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3862" t="inlineStr"/>
+      <c r="C3862" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3863">
+      <c r="A3863" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3863" t="inlineStr"/>
+      <c r="C3863" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3864">
+      <c r="A3864" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3864" t="inlineStr"/>
+      <c r="C3864" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3865">
+      <c r="A3865" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3865" t="inlineStr"/>
+      <c r="C3865" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3866">
+      <c r="A3866" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3866" t="inlineStr"/>
+      <c r="C3866" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3867">
+      <c r="A3867" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3867" t="inlineStr"/>
+      <c r="C3867" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3868">
+      <c r="A3868" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3868" t="inlineStr"/>
+      <c r="C3868" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3869">
+      <c r="A3869" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3869" t="inlineStr"/>
+      <c r="C3869" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3870">
+      <c r="A3870" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3870" t="inlineStr"/>
+      <c r="C3870" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3871">
+      <c r="A3871" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3871" t="inlineStr"/>
+      <c r="C3871" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3872">
+      <c r="A3872" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3872" t="inlineStr"/>
+      <c r="C3872" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3873">
+      <c r="A3873" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3873" t="inlineStr"/>
+      <c r="C3873" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3874">
+      <c r="A3874" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3874" t="inlineStr"/>
+      <c r="C3874" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3875">
+      <c r="A3875" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3875" t="inlineStr"/>
+      <c r="C3875" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3876">
+      <c r="A3876" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3876" t="inlineStr"/>
+      <c r="C3876" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3877">
+      <c r="A3877" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3877" t="inlineStr"/>
+      <c r="C3877" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3878">
+      <c r="A3878" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3878" t="inlineStr"/>
+      <c r="C3878" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3879">
+      <c r="A3879" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3879" t="inlineStr"/>
+      <c r="C3879" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3880">
+      <c r="A3880" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3880" t="inlineStr"/>
+      <c r="C3880" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3881">
+      <c r="A3881" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3881" t="inlineStr"/>
+      <c r="C3881" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3882">
+      <c r="A3882" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3882" t="inlineStr"/>
+      <c r="C3882" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3883">
+      <c r="A3883" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3883" t="inlineStr"/>
+      <c r="C3883" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3884">
+      <c r="A3884" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3884" t="inlineStr"/>
+      <c r="C3884" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3885">
+      <c r="A3885" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3885" t="inlineStr"/>
+      <c r="C3885" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3886">
+      <c r="A3886" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3886" t="inlineStr"/>
+      <c r="C3886" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3887">
+      <c r="A3887" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3887" t="inlineStr"/>
+      <c r="C3887" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3888">
+      <c r="A3888" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3888" t="inlineStr"/>
+      <c r="C3888" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3889">
+      <c r="A3889" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3889" t="inlineStr"/>
+      <c r="C3889" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3890">
+      <c r="A3890" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3890" t="inlineStr"/>
+      <c r="C3890" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3891">
+      <c r="A3891" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3891" t="inlineStr"/>
+      <c r="C3891" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3892">
+      <c r="A3892" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3892" t="inlineStr"/>
+      <c r="C3892" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="3893">
+      <c r="A3893" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3893" t="inlineStr"/>
+      <c r="C3893" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3894">
+      <c r="A3894" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3894" t="inlineStr"/>
+      <c r="C3894" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3895">
+      <c r="A3895" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3895" t="inlineStr"/>
+      <c r="C3895" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3896">
+      <c r="A3896" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3896" t="inlineStr"/>
+      <c r="C3896" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3897">
+      <c r="A3897" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3897" t="inlineStr"/>
+      <c r="C3897" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3898">
+      <c r="A3898" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3898" t="inlineStr"/>
+      <c r="C3898" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3899">
+      <c r="A3899" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3899" t="inlineStr"/>
+      <c r="C3899" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3900">
+      <c r="A3900" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3900" t="inlineStr"/>
+      <c r="C3900" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3901">
+      <c r="A3901" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3901" t="inlineStr"/>
+      <c r="C3901" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3902">
+      <c r="A3902" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3902" t="inlineStr"/>
+      <c r="C3902" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3903">
+      <c r="A3903" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3903" t="inlineStr"/>
+      <c r="C3903" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3904">
+      <c r="A3904" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3904" t="inlineStr"/>
+      <c r="C3904" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3905">
+      <c r="A3905" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3905" t="inlineStr"/>
+      <c r="C3905" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3906">
+      <c r="A3906" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3906" t="inlineStr"/>
+      <c r="C3906" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3907">
+      <c r="A3907" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3907" t="inlineStr"/>
+      <c r="C3907" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3908">
+      <c r="A3908" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3908" t="inlineStr"/>
+      <c r="C3908" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3909">
+      <c r="A3909" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3909" t="inlineStr"/>
+      <c r="C3909" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3910">
+      <c r="A3910" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3910" t="inlineStr"/>
+      <c r="C3910" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3911">
+      <c r="A3911" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3911" t="inlineStr"/>
+      <c r="C3911" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3912">
+      <c r="A3912" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3912" t="inlineStr"/>
+      <c r="C3912" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3913">
+      <c r="A3913" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3913" t="inlineStr"/>
+      <c r="C3913" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3914">
+      <c r="A3914" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3914" t="inlineStr"/>
+      <c r="C3914" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3915">
+      <c r="A3915" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3915" t="inlineStr"/>
+      <c r="C3915" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3916">
+      <c r="A3916" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3916" t="inlineStr"/>
+      <c r="C3916" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3917">
+      <c r="A3917" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3917" t="inlineStr"/>
+      <c r="C3917" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3918">
+      <c r="A3918" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3918" t="inlineStr"/>
+      <c r="C3918" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3919">
+      <c r="A3919" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3919" t="inlineStr"/>
+      <c r="C3919" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3920">
+      <c r="A3920" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3920" t="inlineStr"/>
+      <c r="C3920" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3921">
+      <c r="A3921" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3921" t="inlineStr"/>
+      <c r="C3921" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3922">
+      <c r="A3922" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3922" t="inlineStr"/>
+      <c r="C3922" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3923">
+      <c r="A3923" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3923" t="inlineStr"/>
+      <c r="C3923" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3924">
+      <c r="A3924" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3924" t="inlineStr"/>
+      <c r="C3924" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3925">
+      <c r="A3925" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3925" t="inlineStr"/>
+      <c r="C3925" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3926">
+      <c r="A3926" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3926" t="inlineStr"/>
+      <c r="C3926" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3927">
+      <c r="A3927" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3927" t="inlineStr"/>
+      <c r="C3927" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3928">
+      <c r="A3928" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3928" t="inlineStr"/>
+      <c r="C3928" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3929">
+      <c r="A3929" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3929" t="inlineStr"/>
+      <c r="C3929" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3930">
+      <c r="A3930" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3930" t="inlineStr"/>
+      <c r="C3930" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3931">
+      <c r="A3931" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3931" t="inlineStr"/>
+      <c r="C3931" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3932">
+      <c r="A3932" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3932" t="inlineStr"/>
+      <c r="C3932" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3933">
+      <c r="A3933" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3933" t="inlineStr"/>
+      <c r="C3933" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3934">
+      <c r="A3934" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3934" t="inlineStr"/>
+      <c r="C3934" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3935">
+      <c r="A3935" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3935" t="inlineStr"/>
+      <c r="C3935" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3936">
+      <c r="A3936" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3936" t="inlineStr"/>
+      <c r="C3936" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3937">
+      <c r="A3937" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3937" t="inlineStr"/>
+      <c r="C3937" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3938">
+      <c r="A3938" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3938" t="inlineStr"/>
+      <c r="C3938" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3939">
+      <c r="A3939" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3939" t="inlineStr"/>
+      <c r="C3939" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3940">
+      <c r="A3940" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3940" t="inlineStr"/>
+      <c r="C3940" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3941">
+      <c r="A3941" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3941" t="inlineStr"/>
+      <c r="C3941" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3942">
+      <c r="A3942" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3942" t="inlineStr"/>
+      <c r="C3942" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3943">
+      <c r="A3943" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3943" t="inlineStr"/>
+      <c r="C3943" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3944">
+      <c r="A3944" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3944" t="inlineStr"/>
+      <c r="C3944" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3945">
+      <c r="A3945" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3945" t="inlineStr"/>
+      <c r="C3945" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3946">
+      <c r="A3946" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3946" t="inlineStr"/>
+      <c r="C3946" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3947">
+      <c r="A3947" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3947" t="inlineStr"/>
+      <c r="C3947" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3948">
+      <c r="A3948" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3948" t="inlineStr"/>
+      <c r="C3948" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3949">
+      <c r="A3949" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3949" t="inlineStr"/>
+      <c r="C3949" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3950">
+      <c r="A3950" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3950" t="inlineStr"/>
+      <c r="C3950" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3951">
+      <c r="A3951" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3951" t="inlineStr"/>
+      <c r="C3951" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3952">
+      <c r="A3952" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3952" t="inlineStr"/>
+      <c r="C3952" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3953">
+      <c r="A3953" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3953" t="inlineStr"/>
+      <c r="C3953" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3954">
+      <c r="A3954" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3954" t="inlineStr"/>
+      <c r="C3954" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3955">
+      <c r="A3955" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3955" t="inlineStr"/>
+      <c r="C3955" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3956">
+      <c r="A3956" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3956" t="inlineStr"/>
+      <c r="C3956" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3957">
+      <c r="A3957" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3957" t="inlineStr"/>
+      <c r="C3957" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3958">
+      <c r="A3958" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3958" t="inlineStr"/>
+      <c r="C3958" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3959">
+      <c r="A3959" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3959" t="inlineStr"/>
+      <c r="C3959" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3960">
+      <c r="A3960" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3960" t="inlineStr"/>
+      <c r="C3960" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3961">
+      <c r="A3961" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3961" t="inlineStr"/>
+      <c r="C3961" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3962">
+      <c r="A3962" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3962" t="inlineStr"/>
+      <c r="C3962" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3963">
+      <c r="A3963" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3963" t="inlineStr"/>
+      <c r="C3963" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3964">
+      <c r="A3964" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3964" t="inlineStr"/>
+      <c r="C3964" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3965">
+      <c r="A3965" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B3965" t="inlineStr"/>
+      <c r="C3965" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="3966">
+      <c r="A3966" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3966" t="inlineStr"/>
+      <c r="C3966" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3967">
+      <c r="A3967" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3967" t="inlineStr"/>
+      <c r="C3967" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3968">
+      <c r="A3968" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3968" t="inlineStr"/>
+      <c r="C3968" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3969">
+      <c r="A3969" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3969" t="inlineStr"/>
+      <c r="C3969" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3970">
+      <c r="A3970" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3970" t="inlineStr"/>
+      <c r="C3970" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3971">
+      <c r="A3971" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3971" t="inlineStr"/>
+      <c r="C3971" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3972">
+      <c r="A3972" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3972" t="inlineStr"/>
+      <c r="C3972" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3973">
+      <c r="A3973" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3973" t="inlineStr"/>
+      <c r="C3973" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3974">
+      <c r="A3974" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3974" t="inlineStr"/>
+      <c r="C3974" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3975">
+      <c r="A3975" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3975" t="inlineStr"/>
+      <c r="C3975" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3976">
+      <c r="A3976" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3976" t="inlineStr"/>
+      <c r="C3976" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3977">
+      <c r="A3977" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3977" t="inlineStr"/>
+      <c r="C3977" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3978">
+      <c r="A3978" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3978" t="inlineStr"/>
+      <c r="C3978" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3979">
+      <c r="A3979" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3979" t="inlineStr"/>
+      <c r="C3979" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3980">
+      <c r="A3980" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3980" t="inlineStr"/>
+      <c r="C3980" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3981">
+      <c r="A3981" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3981" t="inlineStr"/>
+      <c r="C3981" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3982">
+      <c r="A3982" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3982" t="inlineStr"/>
+      <c r="C3982" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3983">
+      <c r="A3983" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3983" t="inlineStr"/>
+      <c r="C3983" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3984">
+      <c r="A3984" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3984" t="inlineStr"/>
+      <c r="C3984" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3985">
+      <c r="A3985" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3985" t="inlineStr"/>
+      <c r="C3985" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3986">
+      <c r="A3986" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3986" t="inlineStr"/>
+      <c r="C3986" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3987">
+      <c r="A3987" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3987" t="inlineStr"/>
+      <c r="C3987" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3988">
+      <c r="A3988" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3988" t="inlineStr"/>
+      <c r="C3988" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3989">
+      <c r="A3989" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3989" t="inlineStr"/>
+      <c r="C3989" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3990">
+      <c r="A3990" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B3990" t="inlineStr"/>
+      <c r="C3990" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3991">
+      <c r="A3991" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3991" t="inlineStr"/>
+      <c r="C3991" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3992">
+      <c r="A3992" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3992" t="inlineStr"/>
+      <c r="C3992" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3993">
+      <c r="A3993" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3993" t="inlineStr"/>
+      <c r="C3993" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3994">
+      <c r="A3994" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3994" t="inlineStr"/>
+      <c r="C3994" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3995">
+      <c r="A3995" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3995" t="inlineStr"/>
+      <c r="C3995" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3996">
+      <c r="A3996" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3996" t="inlineStr"/>
+      <c r="C3996" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3997">
+      <c r="A3997" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3997" t="inlineStr"/>
+      <c r="C3997" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3998">
+      <c r="A3998" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3998" t="inlineStr"/>
+      <c r="C3998" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3999">
+      <c r="A3999" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B3999" t="inlineStr"/>
+      <c r="C3999" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4000">
+      <c r="A4000" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4000" t="inlineStr"/>
+      <c r="C4000" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4001">
+      <c r="A4001" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4001" t="inlineStr"/>
+      <c r="C4001" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4002">
+      <c r="A4002" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4002" t="inlineStr"/>
+      <c r="C4002" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4003">
+      <c r="A4003" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4003" t="inlineStr"/>
+      <c r="C4003" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4004">
+      <c r="A4004" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4004" t="inlineStr"/>
+      <c r="C4004" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4005">
+      <c r="A4005" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4005" t="inlineStr"/>
+      <c r="C4005" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4006">
+      <c r="A4006" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4006" t="inlineStr"/>
+      <c r="C4006" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4007">
+      <c r="A4007" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4007" t="inlineStr"/>
+      <c r="C4007" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4008">
+      <c r="A4008" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4008" t="inlineStr"/>
+      <c r="C4008" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4009">
+      <c r="A4009" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4009" t="inlineStr"/>
+      <c r="C4009" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4010">
+      <c r="A4010" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4010" t="inlineStr"/>
+      <c r="C4010" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4011">
+      <c r="A4011" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4011" t="inlineStr"/>
+      <c r="C4011" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4012">
+      <c r="A4012" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4012" t="inlineStr"/>
+      <c r="C4012" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4013">
+      <c r="A4013" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4013" t="inlineStr"/>
+      <c r="C4013" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4014">
+      <c r="A4014" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4014" t="inlineStr"/>
+      <c r="C4014" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4015">
+      <c r="A4015" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4015" t="inlineStr"/>
+      <c r="C4015" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4016">
+      <c r="A4016" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4016" t="inlineStr"/>
+      <c r="C4016" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4017">
+      <c r="A4017" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4017" t="inlineStr"/>
+      <c r="C4017" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4018">
+      <c r="A4018" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4018" t="inlineStr"/>
+      <c r="C4018" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4019">
+      <c r="A4019" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4019" t="inlineStr"/>
+      <c r="C4019" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4020">
+      <c r="A4020" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4020" t="inlineStr"/>
+      <c r="C4020" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4021">
+      <c r="A4021" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4021" t="inlineStr"/>
+      <c r="C4021" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4022">
+      <c r="A4022" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4022" t="inlineStr"/>
+      <c r="C4022" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4023">
+      <c r="A4023" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4023" t="inlineStr"/>
+      <c r="C4023" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4024">
+      <c r="A4024" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4024" t="inlineStr"/>
+      <c r="C4024" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4025">
+      <c r="A4025" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4025" t="inlineStr"/>
+      <c r="C4025" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4026">
+      <c r="A4026" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4026" t="inlineStr"/>
+      <c r="C4026" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4027">
+      <c r="A4027" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4027" t="inlineStr"/>
+      <c r="C4027" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4028">
+      <c r="A4028" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4028" t="inlineStr"/>
+      <c r="C4028" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4029">
+      <c r="A4029" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4029" t="inlineStr"/>
+      <c r="C4029" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4030">
+      <c r="A4030" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4030" t="inlineStr"/>
+      <c r="C4030" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4031">
+      <c r="A4031" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4031" t="inlineStr"/>
+      <c r="C4031" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4032">
+      <c r="A4032" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4032" t="inlineStr"/>
+      <c r="C4032" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4033">
+      <c r="A4033" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4033" t="inlineStr"/>
+      <c r="C4033" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4034">
+      <c r="A4034" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4034" t="inlineStr"/>
+      <c r="C4034" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4035">
+      <c r="A4035" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4035" t="inlineStr"/>
+      <c r="C4035" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4036">
+      <c r="A4036" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4036" t="inlineStr"/>
+      <c r="C4036" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4037">
+      <c r="A4037" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4037" t="inlineStr"/>
+      <c r="C4037" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4038">
+      <c r="A4038" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4038" t="inlineStr"/>
+      <c r="C4038" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="4039">
+      <c r="A4039" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4039" t="inlineStr"/>
+      <c r="C4039" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4040">
+      <c r="A4040" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4040" t="inlineStr"/>
+      <c r="C4040" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4041">
+      <c r="A4041" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4041" t="inlineStr"/>
+      <c r="C4041" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4042">
+      <c r="A4042" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4042" t="inlineStr"/>
+      <c r="C4042" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4043">
+      <c r="A4043" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4043" t="inlineStr"/>
+      <c r="C4043" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4044">
+      <c r="A4044" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4044" t="inlineStr"/>
+      <c r="C4044" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4045">
+      <c r="A4045" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4045" t="inlineStr"/>
+      <c r="C4045" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4046">
+      <c r="A4046" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4046" t="inlineStr"/>
+      <c r="C4046" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4047">
+      <c r="A4047" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4047" t="inlineStr"/>
+      <c r="C4047" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4048">
+      <c r="A4048" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4048" t="inlineStr"/>
+      <c r="C4048" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4049">
+      <c r="A4049" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4049" t="inlineStr"/>
+      <c r="C4049" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4050">
+      <c r="A4050" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4050" t="inlineStr"/>
+      <c r="C4050" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4051">
+      <c r="A4051" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4051" t="inlineStr"/>
+      <c r="C4051" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4052">
+      <c r="A4052" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4052" t="inlineStr"/>
+      <c r="C4052" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4053">
+      <c r="A4053" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4053" t="inlineStr"/>
+      <c r="C4053" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4054">
+      <c r="A4054" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4054" t="inlineStr"/>
+      <c r="C4054" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4055">
+      <c r="A4055" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4055" t="inlineStr"/>
+      <c r="C4055" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4056">
+      <c r="A4056" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4056" t="inlineStr"/>
+      <c r="C4056" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4057">
+      <c r="A4057" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4057" t="inlineStr"/>
+      <c r="C4057" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4058">
+      <c r="A4058" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4058" t="inlineStr"/>
+      <c r="C4058" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4059">
+      <c r="A4059" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4059" t="inlineStr"/>
+      <c r="C4059" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4060">
+      <c r="A4060" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4060" t="inlineStr"/>
+      <c r="C4060" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4061">
+      <c r="A4061" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4061" t="inlineStr"/>
+      <c r="C4061" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4062">
+      <c r="A4062" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4062" t="inlineStr"/>
+      <c r="C4062" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4063">
+      <c r="A4063" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4063" t="inlineStr"/>
+      <c r="C4063" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4064">
+      <c r="A4064" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4064" t="inlineStr"/>
+      <c r="C4064" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4065">
+      <c r="A4065" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4065" t="inlineStr"/>
+      <c r="C4065" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4066">
+      <c r="A4066" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4066" t="inlineStr"/>
+      <c r="C4066" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4067">
+      <c r="A4067" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4067" t="inlineStr"/>
+      <c r="C4067" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4068">
+      <c r="A4068" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4068" t="inlineStr"/>
+      <c r="C4068" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4069">
+      <c r="A4069" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4069" t="inlineStr"/>
+      <c r="C4069" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4070">
+      <c r="A4070" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4070" t="inlineStr"/>
+      <c r="C4070" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4071">
+      <c r="A4071" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4071" t="inlineStr"/>
+      <c r="C4071" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4072">
+      <c r="A4072" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4072" t="inlineStr"/>
+      <c r="C4072" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4073">
+      <c r="A4073" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4073" t="inlineStr"/>
+      <c r="C4073" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4074">
+      <c r="A4074" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4074" t="inlineStr"/>
+      <c r="C4074" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4075">
+      <c r="A4075" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4075" t="inlineStr"/>
+      <c r="C4075" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4076">
+      <c r="A4076" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4076" t="inlineStr"/>
+      <c r="C4076" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4077">
+      <c r="A4077" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4077" t="inlineStr"/>
+      <c r="C4077" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4078">
+      <c r="A4078" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4078" t="inlineStr"/>
+      <c r="C4078" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4079">
+      <c r="A4079" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4079" t="inlineStr"/>
+      <c r="C4079" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4080">
+      <c r="A4080" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4080" t="inlineStr"/>
+      <c r="C4080" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4081">
+      <c r="A4081" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4081" t="inlineStr"/>
+      <c r="C4081" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4082">
+      <c r="A4082" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4082" t="inlineStr"/>
+      <c r="C4082" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4083">
+      <c r="A4083" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4083" t="inlineStr"/>
+      <c r="C4083" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4084">
+      <c r="A4084" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4084" t="inlineStr"/>
+      <c r="C4084" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4085">
+      <c r="A4085" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4085" t="inlineStr"/>
+      <c r="C4085" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4086">
+      <c r="A4086" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4086" t="inlineStr"/>
+      <c r="C4086" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4087">
+      <c r="A4087" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4087" t="inlineStr"/>
+      <c r="C4087" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4088">
+      <c r="A4088" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4088" t="inlineStr"/>
+      <c r="C4088" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4089">
+      <c r="A4089" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4089" t="inlineStr"/>
+      <c r="C4089" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4090">
+      <c r="A4090" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4090" t="inlineStr"/>
+      <c r="C4090" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4091">
+      <c r="A4091" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4091" t="inlineStr"/>
+      <c r="C4091" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4092">
+      <c r="A4092" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4092" t="inlineStr"/>
+      <c r="C4092" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4093">
+      <c r="A4093" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4093" t="inlineStr"/>
+      <c r="C4093" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4094">
+      <c r="A4094" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4094" t="inlineStr"/>
+      <c r="C4094" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4095">
+      <c r="A4095" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4095" t="inlineStr"/>
+      <c r="C4095" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4096">
+      <c r="A4096" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4096" t="inlineStr"/>
+      <c r="C4096" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4097">
+      <c r="A4097" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4097" t="inlineStr"/>
+      <c r="C4097" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4098">
+      <c r="A4098" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4098" t="inlineStr"/>
+      <c r="C4098" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4099">
+      <c r="A4099" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4099" t="inlineStr"/>
+      <c r="C4099" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4100">
+      <c r="A4100" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4100" t="inlineStr"/>
+      <c r="C4100" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4101">
+      <c r="A4101" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4101" t="inlineStr"/>
+      <c r="C4101" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4102">
+      <c r="A4102" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4102" t="inlineStr"/>
+      <c r="C4102" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4103">
+      <c r="A4103" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4103" t="inlineStr"/>
+      <c r="C4103" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4104">
+      <c r="A4104" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4104" t="inlineStr"/>
+      <c r="C4104" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4105">
+      <c r="A4105" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4105" t="inlineStr"/>
+      <c r="C4105" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4106">
+      <c r="A4106" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4106" t="inlineStr"/>
+      <c r="C4106" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4107">
+      <c r="A4107" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4107" t="inlineStr"/>
+      <c r="C4107" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4108">
+      <c r="A4108" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4108" t="inlineStr"/>
+      <c r="C4108" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4109">
+      <c r="A4109" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4109" t="inlineStr"/>
+      <c r="C4109" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4110">
+      <c r="A4110" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4110" t="inlineStr"/>
+      <c r="C4110" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4111">
+      <c r="A4111" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4111" t="inlineStr"/>
+      <c r="C4111" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4112">
+      <c r="A4112" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4112" t="inlineStr"/>
+      <c r="C4112" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4113">
+      <c r="A4113" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4113" t="inlineStr"/>
+      <c r="C4113" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4114">
+      <c r="A4114" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4114" t="inlineStr"/>
+      <c r="C4114" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4115">
+      <c r="A4115" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4115" t="inlineStr"/>
+      <c r="C4115" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4116">
+      <c r="A4116" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4116" t="inlineStr"/>
+      <c r="C4116" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4117">
+      <c r="A4117" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4117" t="inlineStr"/>
+      <c r="C4117" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4118">
+      <c r="A4118" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4118" t="inlineStr"/>
+      <c r="C4118" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4119">
+      <c r="A4119" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4119" t="inlineStr"/>
+      <c r="C4119" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4120">
+      <c r="A4120" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4120" t="inlineStr"/>
+      <c r="C4120" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4121">
+      <c r="A4121" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4121" t="inlineStr"/>
+      <c r="C4121" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4122">
+      <c r="A4122" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4122" t="inlineStr"/>
+      <c r="C4122" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4123">
+      <c r="A4123" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4123" t="inlineStr"/>
+      <c r="C4123" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4124">
+      <c r="A4124" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4124" t="inlineStr"/>
+      <c r="C4124" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4125">
+      <c r="A4125" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4125" t="inlineStr"/>
+      <c r="C4125" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4126">
+      <c r="A4126" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4126" t="inlineStr"/>
+      <c r="C4126" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4127">
+      <c r="A4127" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4127" t="inlineStr"/>
+      <c r="C4127" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4128">
+      <c r="A4128" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4128" t="inlineStr"/>
+      <c r="C4128" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4129">
+      <c r="A4129" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4129" t="inlineStr"/>
+      <c r="C4129" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4130">
+      <c r="A4130" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4130" t="inlineStr"/>
+      <c r="C4130" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4131">
+      <c r="A4131" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4131" t="inlineStr"/>
+      <c r="C4131" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4132">
+      <c r="A4132" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4132" t="inlineStr"/>
+      <c r="C4132" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4133">
+      <c r="A4133" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4133" t="inlineStr"/>
+      <c r="C4133" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4134">
+      <c r="A4134" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4134" t="inlineStr"/>
+      <c r="C4134" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4135">
+      <c r="A4135" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4135" t="inlineStr"/>
+      <c r="C4135" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4136">
+      <c r="A4136" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4136" t="inlineStr"/>
+      <c r="C4136" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4137">
+      <c r="A4137" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4137" t="inlineStr"/>
+      <c r="C4137" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4138">
+      <c r="A4138" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4138" t="inlineStr"/>
+      <c r="C4138" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4139">
+      <c r="A4139" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4139" t="inlineStr"/>
+      <c r="C4139" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4140">
+      <c r="A4140" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4140" t="inlineStr"/>
+      <c r="C4140" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4141">
+      <c r="A4141" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4141" t="inlineStr"/>
+      <c r="C4141" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4142">
+      <c r="A4142" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4142" t="inlineStr"/>
+      <c r="C4142" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4143">
+      <c r="A4143" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4143" t="inlineStr"/>
+      <c r="C4143" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4144">
+      <c r="A4144" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4144" t="inlineStr"/>
+      <c r="C4144" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4145">
+      <c r="A4145" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4145" t="inlineStr"/>
+      <c r="C4145" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4146">
+      <c r="A4146" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4146" t="inlineStr"/>
+      <c r="C4146" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4147">
+      <c r="A4147" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4147" t="inlineStr"/>
+      <c r="C4147" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4148">
+      <c r="A4148" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4148" t="inlineStr"/>
+      <c r="C4148" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4149">
+      <c r="A4149" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4149" t="inlineStr"/>
+      <c r="C4149" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4150">
+      <c r="A4150" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4150" t="inlineStr"/>
+      <c r="C4150" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4151">
+      <c r="A4151" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4151" t="inlineStr"/>
+      <c r="C4151" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4152">
+      <c r="A4152" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4152" t="inlineStr"/>
+      <c r="C4152" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4153">
+      <c r="A4153" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4153" t="inlineStr"/>
+      <c r="C4153" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4154">
+      <c r="A4154" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4154" t="inlineStr"/>
+      <c r="C4154" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4155">
+      <c r="A4155" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4155" t="inlineStr"/>
+      <c r="C4155" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4156">
+      <c r="A4156" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4156" t="inlineStr"/>
+      <c r="C4156" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4157">
+      <c r="A4157" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4157" t="inlineStr"/>
+      <c r="C4157" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4158">
+      <c r="A4158" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4158" t="inlineStr"/>
+      <c r="C4158" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4159">
+      <c r="A4159" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4159" t="inlineStr"/>
+      <c r="C4159" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4160">
+      <c r="A4160" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4160" t="inlineStr"/>
+      <c r="C4160" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4161">
+      <c r="A4161" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4161" t="inlineStr"/>
+      <c r="C4161" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4162">
+      <c r="A4162" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4162" t="inlineStr"/>
+      <c r="C4162" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4163">
+      <c r="A4163" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4163" t="inlineStr"/>
+      <c r="C4163" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4164">
+      <c r="A4164" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4164" t="inlineStr"/>
+      <c r="C4164" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4165">
+      <c r="A4165" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4165" t="inlineStr"/>
+      <c r="C4165" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4166">
+      <c r="A4166" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4166" t="inlineStr"/>
+      <c r="C4166" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4167">
+      <c r="A4167" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4167" t="inlineStr"/>
+      <c r="C4167" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4168">
+      <c r="A4168" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4168" t="inlineStr"/>
+      <c r="C4168" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4169">
+      <c r="A4169" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4169" t="inlineStr"/>
+      <c r="C4169" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4170">
+      <c r="A4170" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4170" t="inlineStr"/>
+      <c r="C4170" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4171">
+      <c r="A4171" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4171" t="inlineStr"/>
+      <c r="C4171" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4172">
+      <c r="A4172" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4172" t="inlineStr"/>
+      <c r="C4172" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4173">
+      <c r="A4173" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4173" t="inlineStr"/>
+      <c r="C4173" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4174">
+      <c r="A4174" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4174" t="inlineStr"/>
+      <c r="C4174" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4175">
+      <c r="A4175" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4175" t="inlineStr"/>
+      <c r="C4175" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4176">
+      <c r="A4176" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4176" t="inlineStr"/>
+      <c r="C4176" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4177">
+      <c r="A4177" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4177" t="inlineStr"/>
+      <c r="C4177" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4178">
+      <c r="A4178" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4178" t="inlineStr"/>
+      <c r="C4178" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4179">
+      <c r="A4179" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4179" t="inlineStr"/>
+      <c r="C4179" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4180">
+      <c r="A4180" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4180" t="inlineStr"/>
+      <c r="C4180" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4181">
+      <c r="A4181" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4181" t="inlineStr"/>
+      <c r="C4181" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4182">
+      <c r="A4182" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4182" t="inlineStr"/>
+      <c r="C4182" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4183">
+      <c r="A4183" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4183" t="inlineStr"/>
+      <c r="C4183" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4184">
+      <c r="A4184" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4184" t="inlineStr"/>
+      <c r="C4184" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4185">
+      <c r="A4185" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4185" t="inlineStr"/>
+      <c r="C4185" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4186">
+      <c r="A4186" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4186" t="inlineStr"/>
+      <c r="C4186" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4187">
+      <c r="A4187" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4187" t="inlineStr"/>
+      <c r="C4187" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4188">
+      <c r="A4188" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4188" t="inlineStr"/>
+      <c r="C4188" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4189">
+      <c r="A4189" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4189" t="inlineStr"/>
+      <c r="C4189" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4190">
+      <c r="A4190" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4190" t="inlineStr"/>
+      <c r="C4190" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4191">
+      <c r="A4191" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4191" t="inlineStr"/>
+      <c r="C4191" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4192">
+      <c r="A4192" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4192" t="inlineStr"/>
+      <c r="C4192" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4193">
+      <c r="A4193" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4193" t="inlineStr"/>
+      <c r="C4193" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4194">
+      <c r="A4194" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4194" t="inlineStr"/>
+      <c r="C4194" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4195">
+      <c r="A4195" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4195" t="inlineStr"/>
+      <c r="C4195" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4196">
+      <c r="A4196" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4196" t="inlineStr"/>
+      <c r="C4196" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4197">
+      <c r="A4197" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4197" t="inlineStr"/>
+      <c r="C4197" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4198">
+      <c r="A4198" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4198" t="inlineStr"/>
+      <c r="C4198" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4199">
+      <c r="A4199" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4199" t="inlineStr"/>
+      <c r="C4199" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4200">
+      <c r="A4200" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4200" t="inlineStr"/>
+      <c r="C4200" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4201">
+      <c r="A4201" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4201" t="inlineStr"/>
+      <c r="C4201" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4202">
+      <c r="A4202" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4202" t="inlineStr"/>
+      <c r="C4202" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4203">
+      <c r="A4203" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4203" t="inlineStr"/>
+      <c r="C4203" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4204">
+      <c r="A4204" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4204" t="inlineStr"/>
+      <c r="C4204" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4205">
+      <c r="A4205" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4205" t="inlineStr"/>
+      <c r="C4205" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4206">
+      <c r="A4206" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4206" t="inlineStr"/>
+      <c r="C4206" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4207">
+      <c r="A4207" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4207" t="inlineStr"/>
+      <c r="C4207" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4208">
+      <c r="A4208" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4208" t="inlineStr"/>
+      <c r="C4208" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4209">
+      <c r="A4209" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4209" t="inlineStr"/>
+      <c r="C4209" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4210">
+      <c r="A4210" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gillett j 
+  aus </t>
+        </is>
+      </c>
+      <c r="C4210" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4211">
+      <c r="A4211" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4211" t="inlineStr"/>
+      <c r="C4211" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4212">
+      <c r="A4212" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4212" t="inlineStr"/>
+      <c r="C4212" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4213">
+      <c r="A4213" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4213" t="inlineStr"/>
+      <c r="C4213" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4214">
+      <c r="A4214" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4214" t="inlineStr"/>
+      <c r="C4214" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4215">
+      <c r="A4215" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4215" t="inlineStr"/>
+      <c r="C4215" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4216">
+      <c r="A4216" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4216" t="inlineStr"/>
+      <c r="C4216" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4217">
+      <c r="A4217" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4217" t="inlineStr"/>
+      <c r="C4217" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4218">
+      <c r="A4218" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4218" t="inlineStr"/>
+      <c r="C4218" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4219">
+      <c r="A4219" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4219" t="inlineStr"/>
+      <c r="C4219" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4220">
+      <c r="A4220" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4220" t="inlineStr"/>
+      <c r="C4220" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4221">
+      <c r="A4221" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4221" t="inlineStr"/>
+      <c r="C4221" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4222">
+      <c r="A4222" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4222" t="inlineStr"/>
+      <c r="C4222" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4223">
+      <c r="A4223" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4223" t="inlineStr"/>
+      <c r="C4223" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4224">
+      <c r="A4224" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4224" t="inlineStr"/>
+      <c r="C4224" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4225">
+      <c r="A4225" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4225" t="inlineStr"/>
+      <c r="C4225" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4226">
+      <c r="A4226" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4226" t="inlineStr"/>
+      <c r="C4226" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4227">
+      <c r="A4227" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4227" t="inlineStr"/>
+      <c r="C4227" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4228">
+      <c r="A4228" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4228" t="inlineStr"/>
+      <c r="C4228" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4229">
+      <c r="A4229" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4229" t="inlineStr"/>
+      <c r="C4229" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4230">
+      <c r="A4230" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4230" t="inlineStr"/>
+      <c r="C4230" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4231">
+      <c r="A4231" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4231" t="inlineStr"/>
+      <c r="C4231" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4232">
+      <c r="A4232" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4232" t="inlineStr"/>
+      <c r="C4232" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4233">
+      <c r="A4233" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4233" t="inlineStr"/>
+      <c r="C4233" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4234">
+      <c r="A4234" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4234" t="inlineStr"/>
+      <c r="C4234" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4235">
+      <c r="A4235" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4235" t="inlineStr"/>
+      <c r="C4235" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4236">
+      <c r="A4236" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4236" t="inlineStr"/>
+      <c r="C4236" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4237">
+      <c r="A4237" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4237" t="inlineStr"/>
+      <c r="C4237" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4238">
+      <c r="A4238" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4238" t="inlineStr"/>
+      <c r="C4238" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4239">
+      <c r="A4239" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4239" t="inlineStr"/>
+      <c r="C4239" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4240">
+      <c r="A4240" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4240" t="inlineStr"/>
+      <c r="C4240" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4241">
+      <c r="A4241" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4241" t="inlineStr"/>
+      <c r="C4241" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4242">
+      <c r="A4242" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4242" t="inlineStr"/>
+      <c r="C4242" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4243">
+      <c r="A4243" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4243" t="inlineStr"/>
+      <c r="C4243" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4244">
+      <c r="A4244" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4244" t="inlineStr"/>
+      <c r="C4244" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4245">
+      <c r="A4245" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4245" t="inlineStr"/>
+      <c r="C4245" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4246">
+      <c r="A4246" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4246" t="inlineStr"/>
+      <c r="C4246" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4247">
+      <c r="A4247" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4247" t="inlineStr"/>
+      <c r="C4247" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4248">
+      <c r="A4248" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4248" t="inlineStr"/>
+      <c r="C4248" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4249">
+      <c r="A4249" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4249" t="inlineStr"/>
+      <c r="C4249" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4250">
+      <c r="A4250" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4250" t="inlineStr"/>
+      <c r="C4250" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4251">
+      <c r="A4251" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4251" t="inlineStr"/>
+      <c r="C4251" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4252">
+      <c r="A4252" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4252" t="inlineStr"/>
+      <c r="C4252" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4253">
+      <c r="A4253" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4253" t="inlineStr"/>
+      <c r="C4253" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4254">
+      <c r="A4254" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4254" t="inlineStr"/>
+      <c r="C4254" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4255">
+      <c r="A4255" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4255" t="inlineStr"/>
+      <c r="C4255" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4256">
+      <c r="A4256" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4256" t="inlineStr"/>
+      <c r="C4256" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4257">
+      <c r="A4257" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4257" t="inlineStr"/>
+      <c r="C4257" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4258">
+      <c r="A4258" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4258" t="inlineStr"/>
+      <c r="C4258" t="n">
+        <v>445</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4258"/>
+  <dimension ref="A1:C4332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58754,6 +58754,825 @@
         <v>445</v>
       </c>
     </row>
+    <row r="4259">
+      <c r="A4259" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4259" t="inlineStr"/>
+      <c r="C4259" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4260">
+      <c r="A4260" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4260" t="inlineStr"/>
+      <c r="C4260" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4261">
+      <c r="A4261" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4261" t="inlineStr"/>
+      <c r="C4261" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4262">
+      <c r="A4262" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4262" t="inlineStr"/>
+      <c r="C4262" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4263">
+      <c r="A4263" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4263" t="inlineStr"/>
+      <c r="C4263" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4264">
+      <c r="A4264" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4264" t="inlineStr"/>
+      <c r="C4264" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4265">
+      <c r="A4265" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4265" t="inlineStr"/>
+      <c r="C4265" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4266">
+      <c r="A4266" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4266" t="inlineStr"/>
+      <c r="C4266" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4267">
+      <c r="A4267" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4267" t="inlineStr"/>
+      <c r="C4267" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4268">
+      <c r="A4268" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4268" t="inlineStr"/>
+      <c r="C4268" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4269">
+      <c r="A4269" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4269" t="inlineStr"/>
+      <c r="C4269" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4270">
+      <c r="A4270" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4270" t="inlineStr"/>
+      <c r="C4270" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4271">
+      <c r="A4271" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4271" t="inlineStr"/>
+      <c r="C4271" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4272">
+      <c r="A4272" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4272" t="inlineStr"/>
+      <c r="C4272" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4273">
+      <c r="A4273" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4273" t="inlineStr"/>
+      <c r="C4273" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4274" t="inlineStr"/>
+      <c r="C4274" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4275" t="inlineStr"/>
+      <c r="C4275" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4276" t="inlineStr"/>
+      <c r="C4276" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4277" t="inlineStr"/>
+      <c r="C4277" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4278" t="inlineStr"/>
+      <c r="C4278" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4279" t="inlineStr"/>
+      <c r="C4279" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4280" t="inlineStr"/>
+      <c r="C4280" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4281">
+      <c r="A4281" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4281" t="inlineStr"/>
+      <c r="C4281" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4282">
+      <c r="A4282" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4282" t="inlineStr"/>
+      <c r="C4282" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4283" t="inlineStr"/>
+      <c r="C4283" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4284">
+      <c r="A4284" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the brick community stadium
+  wigan </t>
+        </is>
+      </c>
+      <c r="C4284" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4285" t="inlineStr"/>
+      <c r="C4285" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4286">
+      <c r="A4286" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4286" t="inlineStr"/>
+      <c r="C4286" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4287" t="inlineStr"/>
+      <c r="C4287" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4288" t="inlineStr"/>
+      <c r="C4288" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4289" t="inlineStr"/>
+      <c r="C4289" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4290">
+      <c r="A4290" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4290" t="inlineStr"/>
+      <c r="C4290" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4291">
+      <c r="A4291" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4291" t="inlineStr"/>
+      <c r="C4291" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4292">
+      <c r="A4292" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4292" t="inlineStr"/>
+      <c r="C4292" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4293">
+      <c r="A4293" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4293" t="inlineStr"/>
+      <c r="C4293" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4294">
+      <c r="A4294" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4294" t="inlineStr"/>
+      <c r="C4294" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4295">
+      <c r="A4295" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4295" t="inlineStr"/>
+      <c r="C4295" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4296">
+      <c r="A4296" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4296" t="inlineStr"/>
+      <c r="C4296" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4297">
+      <c r="A4297" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4297" t="inlineStr"/>
+      <c r="C4297" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4298">
+      <c r="A4298" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4298" t="inlineStr"/>
+      <c r="C4298" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4299">
+      <c r="A4299" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4299" t="inlineStr"/>
+      <c r="C4299" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4300">
+      <c r="A4300" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4300" t="inlineStr"/>
+      <c r="C4300" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4301">
+      <c r="A4301" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4301" t="inlineStr"/>
+      <c r="C4301" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4302">
+      <c r="A4302" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4302" t="inlineStr"/>
+      <c r="C4302" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4303" t="inlineStr"/>
+      <c r="C4303" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4304" t="inlineStr"/>
+      <c r="C4304" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4305" t="inlineStr"/>
+      <c r="C4305" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4306" t="inlineStr"/>
+      <c r="C4306" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4307">
+      <c r="A4307" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4307" t="inlineStr"/>
+      <c r="C4307" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4308" t="inlineStr"/>
+      <c r="C4308" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4309" t="inlineStr"/>
+      <c r="C4309" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4310">
+      <c r="A4310" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4310" t="inlineStr"/>
+      <c r="C4310" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4311">
+      <c r="A4311" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4311" t="inlineStr"/>
+      <c r="C4311" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4312">
+      <c r="A4312" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4312" t="inlineStr"/>
+      <c r="C4312" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4313">
+      <c r="A4313" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4313" t="inlineStr"/>
+      <c r="C4313" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4314">
+      <c r="A4314" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4314" t="inlineStr"/>
+      <c r="C4314" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4315">
+      <c r="A4315" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4315" t="inlineStr"/>
+      <c r="C4315" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4316" t="inlineStr"/>
+      <c r="C4316" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4317">
+      <c r="A4317" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4317" t="inlineStr"/>
+      <c r="C4317" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4318" t="inlineStr"/>
+      <c r="C4318" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4319" t="inlineStr"/>
+      <c r="C4319" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4320">
+      <c r="A4320" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4320" t="inlineStr"/>
+      <c r="C4320" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4321">
+      <c r="A4321" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4321" t="inlineStr"/>
+      <c r="C4321" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4322">
+      <c r="A4322" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4322" t="inlineStr"/>
+      <c r="C4322" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4323">
+      <c r="A4323" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4323" t="inlineStr"/>
+      <c r="C4323" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4324">
+      <c r="A4324" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4324" t="inlineStr"/>
+      <c r="C4324" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4325">
+      <c r="A4325" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4325" t="inlineStr"/>
+      <c r="C4325" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4326">
+      <c r="A4326" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4326" t="inlineStr"/>
+      <c r="C4326" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4327">
+      <c r="A4327" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4327" t="inlineStr"/>
+      <c r="C4327" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4328">
+      <c r="A4328" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4328" t="inlineStr"/>
+      <c r="C4328" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4329">
+      <c r="A4329" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4329" t="inlineStr"/>
+      <c r="C4329" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4330">
+      <c r="A4330" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4330" t="inlineStr"/>
+      <c r="C4330" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4331">
+      <c r="A4331" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4331" t="inlineStr"/>
+      <c r="C4331" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4332">
+      <c r="A4332" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4332" t="inlineStr"/>
+      <c r="C4332" t="n">
+        <v>446</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4258"/>
+  <dimension ref="A1:C4306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58754,6 +58754,534 @@
         <v>445</v>
       </c>
     </row>
+    <row r="4259">
+      <c r="A4259" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4259" t="inlineStr"/>
+      <c r="C4259" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4260">
+      <c r="A4260" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4260" t="inlineStr"/>
+      <c r="C4260" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4261">
+      <c r="A4261" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4261" t="inlineStr"/>
+      <c r="C4261" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4262">
+      <c r="A4262" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4262" t="inlineStr"/>
+      <c r="C4262" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4263">
+      <c r="A4263" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4263" t="inlineStr"/>
+      <c r="C4263" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4264">
+      <c r="A4264" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4264" t="inlineStr"/>
+      <c r="C4264" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4265">
+      <c r="A4265" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4265" t="inlineStr"/>
+      <c r="C4265" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4266">
+      <c r="A4266" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4266" t="inlineStr"/>
+      <c r="C4266" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4267">
+      <c r="A4267" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4267" t="inlineStr"/>
+      <c r="C4267" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4268">
+      <c r="A4268" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4268" t="inlineStr"/>
+      <c r="C4268" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4269">
+      <c r="A4269" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4269" t="inlineStr"/>
+      <c r="C4269" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4270">
+      <c r="A4270" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4270" t="inlineStr"/>
+      <c r="C4270" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4271">
+      <c r="A4271" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4271" t="inlineStr"/>
+      <c r="C4271" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4272">
+      <c r="A4272" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4272" t="inlineStr"/>
+      <c r="C4272" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4273">
+      <c r="A4273" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4273" t="inlineStr"/>
+      <c r="C4273" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4274">
+      <c r="A4274" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4274" t="inlineStr"/>
+      <c r="C4274" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4275">
+      <c r="A4275" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4275" t="inlineStr"/>
+      <c r="C4275" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4276">
+      <c r="A4276" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4276" t="inlineStr"/>
+      <c r="C4276" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4277">
+      <c r="A4277" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4277" t="inlineStr"/>
+      <c r="C4277" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4278">
+      <c r="A4278" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4278" t="inlineStr"/>
+      <c r="C4278" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4279">
+      <c r="A4279" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4279" t="inlineStr"/>
+      <c r="C4279" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4280">
+      <c r="A4280" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4280" t="inlineStr"/>
+      <c r="C4280" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4281">
+      <c r="A4281" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4281" t="inlineStr"/>
+      <c r="C4281" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4282">
+      <c r="A4282" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4282" t="inlineStr"/>
+      <c r="C4282" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4283">
+      <c r="A4283" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4283" t="inlineStr"/>
+      <c r="C4283" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4284">
+      <c r="A4284" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4284" t="inlineStr"/>
+      <c r="C4284" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4285">
+      <c r="A4285" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4285" t="inlineStr"/>
+      <c r="C4285" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4286">
+      <c r="A4286" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4286" t="inlineStr"/>
+      <c r="C4286" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4287">
+      <c r="A4287" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4287" t="inlineStr"/>
+      <c r="C4287" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4288">
+      <c r="A4288" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4288" t="inlineStr"/>
+      <c r="C4288" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4289">
+      <c r="A4289" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4289" t="inlineStr"/>
+      <c r="C4289" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4290">
+      <c r="A4290" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4290" t="inlineStr"/>
+      <c r="C4290" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4291">
+      <c r="A4291" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4291" t="inlineStr"/>
+      <c r="C4291" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4292">
+      <c r="A4292" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4292" t="inlineStr"/>
+      <c r="C4292" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4293">
+      <c r="A4293" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4293" t="inlineStr"/>
+      <c r="C4293" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4294">
+      <c r="A4294" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4294" t="inlineStr"/>
+      <c r="C4294" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4295">
+      <c r="A4295" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4295" t="inlineStr"/>
+      <c r="C4295" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4296">
+      <c r="A4296" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4296" t="inlineStr"/>
+      <c r="C4296" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4297">
+      <c r="A4297" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4297" t="inlineStr"/>
+      <c r="C4297" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4298">
+      <c r="A4298" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4298" t="inlineStr"/>
+      <c r="C4298" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4299">
+      <c r="A4299" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4299" t="inlineStr"/>
+      <c r="C4299" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4300">
+      <c r="A4300" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4300" t="inlineStr"/>
+      <c r="C4300" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4301">
+      <c r="A4301" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4301" t="inlineStr"/>
+      <c r="C4301" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4302">
+      <c r="A4302" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4302" t="inlineStr"/>
+      <c r="C4302" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4303">
+      <c r="A4303" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4303" t="inlineStr"/>
+      <c r="C4303" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4304">
+      <c r="A4304" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4304" t="inlineStr"/>
+      <c r="C4304" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4305">
+      <c r="A4305" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4305" t="inlineStr"/>
+      <c r="C4305" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4306">
+      <c r="A4306" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4306" t="inlineStr"/>
+      <c r="C4306" t="n">
+        <v>446</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4306"/>
+  <dimension ref="A1:C4455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59282,6 +59282,1687 @@
         <v>446</v>
       </c>
     </row>
+    <row r="4307">
+      <c r="A4307" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allison s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4307" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4308">
+      <c r="A4308" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4308" t="inlineStr"/>
+      <c r="C4308" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4309">
+      <c r="A4309" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4309" t="inlineStr"/>
+      <c r="C4309" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4310">
+      <c r="A4310" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4310" t="inlineStr"/>
+      <c r="C4310" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4311">
+      <c r="A4311" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">davies a 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4311" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4312">
+      <c r="A4312" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4312" t="inlineStr"/>
+      <c r="C4312" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4313">
+      <c r="A4313" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4313" t="inlineStr"/>
+      <c r="C4313" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4314">
+      <c r="A4314" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4314" t="inlineStr"/>
+      <c r="C4314" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4315">
+      <c r="A4315" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busby j 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4315" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4316">
+      <c r="A4316" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4316" t="inlineStr"/>
+      <c r="C4316" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4317">
+      <c r="A4317" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4317" t="inlineStr"/>
+      <c r="C4317" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4318">
+      <c r="A4318" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4318" t="inlineStr"/>
+      <c r="C4318" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4319">
+      <c r="A4319" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4319" t="inlineStr"/>
+      <c r="C4319" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4320">
+      <c r="A4320" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4320" t="inlineStr"/>
+      <c r="C4320" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4321">
+      <c r="A4321" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4321" t="inlineStr"/>
+      <c r="C4321" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4322">
+      <c r="A4322" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4322" t="inlineStr"/>
+      <c r="C4322" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4323">
+      <c r="A4323" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4323" t="inlineStr"/>
+      <c r="C4323" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4324">
+      <c r="A4324" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4324" t="inlineStr"/>
+      <c r="C4324" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4325">
+      <c r="A4325" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4325" t="inlineStr"/>
+      <c r="C4325" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4326">
+      <c r="A4326" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4326" t="inlineStr"/>
+      <c r="C4326" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4327">
+      <c r="A4327" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4327" t="inlineStr"/>
+      <c r="C4327" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4328">
+      <c r="A4328" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4328" t="inlineStr"/>
+      <c r="C4328" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4329">
+      <c r="A4329" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4329" t="inlineStr"/>
+      <c r="C4329" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4330">
+      <c r="A4330" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4330" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4331">
+      <c r="A4331" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4331" t="inlineStr"/>
+      <c r="C4331" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4332">
+      <c r="A4332" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4332" t="inlineStr"/>
+      <c r="C4332" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4333">
+      <c r="A4333" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4333" t="inlineStr"/>
+      <c r="C4333" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4334">
+      <c r="A4334" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">webb d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4334" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4335">
+      <c r="A4335" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4335" t="inlineStr"/>
+      <c r="C4335" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4336">
+      <c r="A4336" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4336" t="inlineStr"/>
+      <c r="C4336" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4337">
+      <c r="A4337" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the brick community stadium
+  wigan </t>
+        </is>
+      </c>
+      <c r="C4337" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4338">
+      <c r="A4338" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4338" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="C4338" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4339">
+      <c r="A4339" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4339" t="inlineStr"/>
+      <c r="C4339" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4340">
+      <c r="A4340" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4340" t="inlineStr"/>
+      <c r="C4340" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4341">
+      <c r="A4341" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4341" t="inlineStr"/>
+      <c r="C4341" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4342">
+      <c r="A4342" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4342" t="inlineStr"/>
+      <c r="C4342" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4343">
+      <c r="A4343" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4343" t="inlineStr"/>
+      <c r="C4343" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4344">
+      <c r="A4344" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4344" t="inlineStr"/>
+      <c r="C4344" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4345">
+      <c r="A4345" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4345" t="inlineStr"/>
+      <c r="C4345" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4346">
+      <c r="A4346" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4346" t="inlineStr"/>
+      <c r="C4346" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4347">
+      <c r="A4347" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4347" t="inlineStr"/>
+      <c r="C4347" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4348">
+      <c r="A4348" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4348" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="C4348" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4349">
+      <c r="A4349" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4349" t="inlineStr"/>
+      <c r="C4349" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4350">
+      <c r="A4350" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4350" t="inlineStr"/>
+      <c r="C4350" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4351">
+      <c r="A4351" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4351" t="inlineStr"/>
+      <c r="C4351" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4352">
+      <c r="A4352" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4352" t="inlineStr"/>
+      <c r="C4352" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4353">
+      <c r="A4353" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4353" t="inlineStr"/>
+      <c r="C4353" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4354">
+      <c r="A4354" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4354" t="inlineStr"/>
+      <c r="C4354" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4355">
+      <c r="A4355" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4355" t="inlineStr"/>
+      <c r="C4355" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4356">
+      <c r="A4356" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4356" t="inlineStr"/>
+      <c r="C4356" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4357">
+      <c r="A4357" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4357" t="inlineStr"/>
+      <c r="C4357" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4358">
+      <c r="A4358" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4358" t="inlineStr"/>
+      <c r="C4358" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4359">
+      <c r="A4359" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4359" t="inlineStr"/>
+      <c r="C4359" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4360">
+      <c r="A4360" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4360" t="inlineStr"/>
+      <c r="C4360" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4361">
+      <c r="A4361" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4361" t="inlineStr"/>
+      <c r="C4361" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4362">
+      <c r="A4362" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4362" t="inlineStr"/>
+      <c r="C4362" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4363">
+      <c r="A4363" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4363" t="inlineStr">
+        <is>
+          <t>pYaUUJs1</t>
+        </is>
+      </c>
+      <c r="C4363" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4364">
+      <c r="A4364" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4364" t="inlineStr"/>
+      <c r="C4364" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4365">
+      <c r="A4365" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4365" t="inlineStr"/>
+      <c r="C4365" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4366">
+      <c r="A4366" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4366" t="inlineStr"/>
+      <c r="C4366" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4367">
+      <c r="A4367" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4367" t="inlineStr"/>
+      <c r="C4367" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4368">
+      <c r="A4368" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4368" t="inlineStr"/>
+      <c r="C4368" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4369">
+      <c r="A4369" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4369" t="inlineStr"/>
+      <c r="C4369" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4370">
+      <c r="A4370" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4370" t="inlineStr"/>
+      <c r="C4370" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4371">
+      <c r="A4371" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4371" t="inlineStr"/>
+      <c r="C4371" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4372">
+      <c r="A4372" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4372" t="inlineStr"/>
+      <c r="C4372" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4373">
+      <c r="A4373" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4373" t="inlineStr"/>
+      <c r="C4373" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4374">
+      <c r="A4374" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4374" t="inlineStr"/>
+      <c r="C4374" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4375">
+      <c r="A4375" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4375" t="inlineStr"/>
+      <c r="C4375" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4376">
+      <c r="A4376" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4376" t="inlineStr"/>
+      <c r="C4376" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4377">
+      <c r="A4377" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4377" t="inlineStr"/>
+      <c r="C4377" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4378">
+      <c r="A4378" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4378" t="inlineStr"/>
+      <c r="C4378" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4379">
+      <c r="A4379" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4379" t="inlineStr"/>
+      <c r="C4379" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4380">
+      <c r="A4380" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4380" t="inlineStr"/>
+      <c r="C4380" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4381">
+      <c r="A4381" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4381" t="inlineStr"/>
+      <c r="C4381" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4382">
+      <c r="A4382" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4382" t="inlineStr"/>
+      <c r="C4382" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4383">
+      <c r="A4383" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4383" t="inlineStr"/>
+      <c r="C4383" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4384">
+      <c r="A4384" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4384" t="inlineStr"/>
+      <c r="C4384" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4385">
+      <c r="A4385" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4385" t="inlineStr"/>
+      <c r="C4385" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="4386">
+      <c r="A4386" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4386" t="inlineStr"/>
+      <c r="C4386" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4387">
+      <c r="A4387" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4387" t="inlineStr"/>
+      <c r="C4387" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4388">
+      <c r="A4388" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4388" t="inlineStr"/>
+      <c r="C4388" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4389">
+      <c r="A4389" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4389" t="inlineStr"/>
+      <c r="C4389" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4390">
+      <c r="A4390" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4390" t="inlineStr"/>
+      <c r="C4390" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4391">
+      <c r="A4391" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4391" t="inlineStr"/>
+      <c r="C4391" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4392">
+      <c r="A4392" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4392" t="inlineStr"/>
+      <c r="C4392" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4393">
+      <c r="A4393" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4393" t="inlineStr"/>
+      <c r="C4393" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4394">
+      <c r="A4394" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4394" t="inlineStr"/>
+      <c r="C4394" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4395">
+      <c r="A4395" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4395" t="inlineStr"/>
+      <c r="C4395" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4396">
+      <c r="A4396" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4396" t="inlineStr"/>
+      <c r="C4396" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4397">
+      <c r="A4397" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4397" t="inlineStr"/>
+      <c r="C4397" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4398">
+      <c r="A4398" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4398" t="inlineStr"/>
+      <c r="C4398" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4399">
+      <c r="A4399" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4399" t="inlineStr"/>
+      <c r="C4399" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4400">
+      <c r="A4400" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4400" t="inlineStr"/>
+      <c r="C4400" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4401">
+      <c r="A4401" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4401" t="inlineStr"/>
+      <c r="C4401" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4402">
+      <c r="A4402" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4402" t="inlineStr"/>
+      <c r="C4402" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4403">
+      <c r="A4403" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4403" t="inlineStr"/>
+      <c r="C4403" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4404">
+      <c r="A4404" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4404" t="inlineStr"/>
+      <c r="C4404" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4405">
+      <c r="A4405" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4405" t="inlineStr"/>
+      <c r="C4405" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4406">
+      <c r="A4406" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4406" t="inlineStr"/>
+      <c r="C4406" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4407">
+      <c r="A4407" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4407" t="inlineStr"/>
+      <c r="C4407" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4408">
+      <c r="A4408" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4408" t="inlineStr"/>
+      <c r="C4408" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4409">
+      <c r="A4409" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4409" t="inlineStr"/>
+      <c r="C4409" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4410">
+      <c r="A4410" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4410" t="inlineStr"/>
+      <c r="C4410" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4411">
+      <c r="A4411" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4411" t="inlineStr"/>
+      <c r="C4411" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4412">
+      <c r="A4412" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4412" t="inlineStr"/>
+      <c r="C4412" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4413">
+      <c r="A4413" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4413" t="inlineStr"/>
+      <c r="C4413" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4414">
+      <c r="A4414" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4414" t="inlineStr"/>
+      <c r="C4414" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4415">
+      <c r="A4415" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4415" t="inlineStr"/>
+      <c r="C4415" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4416">
+      <c r="A4416" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4416" t="inlineStr"/>
+      <c r="C4416" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4417">
+      <c r="A4417" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4417" t="inlineStr"/>
+      <c r="C4417" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4418">
+      <c r="A4418" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4418" t="inlineStr"/>
+      <c r="C4418" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4419">
+      <c r="A4419" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4419" t="inlineStr"/>
+      <c r="C4419" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4420">
+      <c r="A4420" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4420" t="inlineStr"/>
+      <c r="C4420" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4421">
+      <c r="A4421" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4421" t="inlineStr"/>
+      <c r="C4421" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4422">
+      <c r="A4422" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4422" t="inlineStr"/>
+      <c r="C4422" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4423">
+      <c r="A4423" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4423" t="inlineStr"/>
+      <c r="C4423" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4424">
+      <c r="A4424" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4424" t="inlineStr"/>
+      <c r="C4424" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4425">
+      <c r="A4425" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4425" t="inlineStr"/>
+      <c r="C4425" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4426">
+      <c r="A4426" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4426" t="inlineStr"/>
+      <c r="C4426" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4427">
+      <c r="A4427" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4427" t="inlineStr"/>
+      <c r="C4427" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4428">
+      <c r="A4428" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4428" t="inlineStr"/>
+      <c r="C4428" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4429">
+      <c r="A4429" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4429" t="inlineStr"/>
+      <c r="C4429" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4430">
+      <c r="A4430" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4430" t="inlineStr"/>
+      <c r="C4430" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4431">
+      <c r="A4431" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4431" t="inlineStr"/>
+      <c r="C4431" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4432">
+      <c r="A4432" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4432" t="inlineStr"/>
+      <c r="C4432" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4433">
+      <c r="A4433" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4433" t="inlineStr"/>
+      <c r="C4433" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4434">
+      <c r="A4434" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4434" t="inlineStr"/>
+      <c r="C4434" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4435">
+      <c r="A4435" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4435" t="inlineStr"/>
+      <c r="C4435" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4436">
+      <c r="A4436" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4436" t="inlineStr"/>
+      <c r="C4436" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4437">
+      <c r="A4437" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4437" t="inlineStr"/>
+      <c r="C4437" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4438">
+      <c r="A4438" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4438" t="inlineStr"/>
+      <c r="C4438" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4439">
+      <c r="A4439" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4439" t="inlineStr"/>
+      <c r="C4439" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4440">
+      <c r="A4440" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4440" t="inlineStr"/>
+      <c r="C4440" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4441">
+      <c r="A4441" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4441" t="inlineStr"/>
+      <c r="C4441" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4442">
+      <c r="A4442" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4442" t="inlineStr"/>
+      <c r="C4442" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4443">
+      <c r="A4443" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4443" t="inlineStr"/>
+      <c r="C4443" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4444">
+      <c r="A4444" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4444" t="inlineStr"/>
+      <c r="C4444" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4445">
+      <c r="A4445" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4445" t="inlineStr"/>
+      <c r="C4445" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4446">
+      <c r="A4446" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4446" t="inlineStr"/>
+      <c r="C4446" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4447">
+      <c r="A4447" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4447" t="inlineStr"/>
+      <c r="C4447" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4448">
+      <c r="A4448" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4448" t="inlineStr"/>
+      <c r="C4448" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4449">
+      <c r="A4449" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4449" t="inlineStr"/>
+      <c r="C4449" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4450">
+      <c r="A4450" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4450" t="inlineStr"/>
+      <c r="C4450" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4451">
+      <c r="A4451" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4451" t="inlineStr"/>
+      <c r="C4451" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4452">
+      <c r="A4452" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4452" t="inlineStr"/>
+      <c r="C4452" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4453">
+      <c r="A4453" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4453" t="inlineStr"/>
+      <c r="C4453" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4454">
+      <c r="A4454" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4454" t="inlineStr"/>
+      <c r="C4454" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="4455">
+      <c r="A4455" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4455" t="inlineStr"/>
+      <c r="C4455" t="n">
+        <v>448</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4455"/>
+  <dimension ref="A1:C4499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60963,6 +60963,697 @@
         <v>448</v>
       </c>
     </row>
+    <row r="4456">
+      <c r="A4456" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4456" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4457">
+      <c r="A4457" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4457" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4458">
+      <c r="A4458" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkinson b 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4458" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4459">
+      <c r="A4459" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salisbury m 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4459" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4460">
+      <c r="A4460" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">martin s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4460" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4461">
+      <c r="A4461" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nield t 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4461" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4462">
+      <c r="A4462" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doughty l 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4462" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4463">
+      <c r="A4463" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mather s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4463" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4464">
+      <c r="A4464" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simpson s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4464" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4465">
+      <c r="A4465" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hicks c 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4465" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4466">
+      <c r="A4466" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4466" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4467">
+      <c r="A4467" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stockbridge s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4467" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4468">
+      <c r="A4468" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oldham s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4468" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4469">
+      <c r="A4469" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4469" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4470">
+      <c r="A4470" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">herczeg a 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4470" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4471">
+      <c r="A4471" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4471" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4472">
+      <c r="A4472" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bourne d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4472" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4473">
+      <c r="A4473" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4473" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4474">
+      <c r="A4474" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley r 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4474" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4475">
+      <c r="A4475" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corlett m 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4475" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4476">
+      <c r="A4476" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4476" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4477">
+      <c r="A4477" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4477" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4478">
+      <c r="A4478" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">envirovent stadium
+  harrogate </t>
+        </is>
+      </c>
+      <c r="C4478" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4479">
+      <c r="A4479" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
+        </is>
+      </c>
+      <c r="C4479" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4480">
+      <c r="A4480" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the den
+  london </t>
+        </is>
+      </c>
+      <c r="C4480" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4481">
+      <c r="A4481" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loftus road
+  london </t>
+        </is>
+      </c>
+      <c r="C4481" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4482">
+      <c r="A4482" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oakwell
+  barnsley </t>
+        </is>
+      </c>
+      <c r="C4482" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4483">
+      <c r="A4483" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coventry building society arena
+  coventry </t>
+        </is>
+      </c>
+      <c r="C4483" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4484">
+      <c r="A4484" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  andrew s stadium
+  birmingham </t>
+        </is>
+      </c>
+      <c r="C4484" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4485">
+      <c r="A4485" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
+        </is>
+      </c>
+      <c r="C4485" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4486">
+      <c r="A4486" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the cherry red records stadium
+  london </t>
+        </is>
+      </c>
+      <c r="C4486" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4487">
+      <c r="A4487" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4487" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="C4487" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4488">
+      <c r="A4488" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4488" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="C4488" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4489">
+      <c r="A4489" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4489" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="C4489" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4490">
+      <c r="A4490" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4490" t="inlineStr">
+        <is>
+          <t>dKVYSSZa</t>
+        </is>
+      </c>
+      <c r="C4490" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4491">
+      <c r="A4491" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4491" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="C4491" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4492">
+      <c r="A4492" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4492" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="C4492" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4493">
+      <c r="A4493" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4493" t="inlineStr">
+        <is>
+          <t>dtwAbyJ5</t>
+        </is>
+      </c>
+      <c r="C4493" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4494">
+      <c r="A4494" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4494" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="C4494" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4495">
+      <c r="A4495" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4495" t="inlineStr">
+        <is>
+          <t>pQTmYFAh</t>
+        </is>
+      </c>
+      <c r="C4495" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4496">
+      <c r="A4496" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4496" t="inlineStr">
+        <is>
+          <t>6watkf6m</t>
+        </is>
+      </c>
+      <c r="C4496" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4497">
+      <c r="A4497" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4497" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="C4497" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4498">
+      <c r="A4498" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4498" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="C4498" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4499">
+      <c r="A4499" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4499" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="C4499" t="n">
+        <v>449</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4455"/>
+  <dimension ref="A1:C4499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60963,6 +60963,697 @@
         <v>448</v>
       </c>
     </row>
+    <row r="4456">
+      <c r="A4456" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4456" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4457">
+      <c r="A4457" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4457" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4457" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4458">
+      <c r="A4458" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bourne d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4458" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4459">
+      <c r="A4459" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">salisbury m 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4459" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4460">
+      <c r="A4460" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4460" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4460" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4461">
+      <c r="A4461" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4461" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mather s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4461" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4462">
+      <c r="A4462" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hicks c 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4462" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4463">
+      <c r="A4463" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">whitestone d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4463" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4464">
+      <c r="A4464" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">doughty l 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4464" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4465">
+      <c r="A4465" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">herczeg a 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4465" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4466">
+      <c r="A4466" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">simpson s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4466" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4467">
+      <c r="A4467" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oldham s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4467" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4468">
+      <c r="A4468" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4468" t="inlineStr">
+        <is>
+          <t xml:space="preserve">madley r 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4468" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4469">
+      <c r="A4469" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coote d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4469" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4470">
+      <c r="A4470" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">martin s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4470" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4471">
+      <c r="A4471" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkinson b 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4471" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4472">
+      <c r="A4472" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corlett m 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4472" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4473">
+      <c r="A4473" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4473" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stockbridge s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4473" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4474">
+      <c r="A4474" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">backhouse a 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4474" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4475">
+      <c r="A4475" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nield t 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4475" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4476">
+      <c r="A4476" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harrington t 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4476" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4477">
+      <c r="A4477" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4477" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jones r 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4477" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4478">
+      <c r="A4478" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the cherry red records stadium
+  london </t>
+        </is>
+      </c>
+      <c r="C4478" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4479">
+      <c r="A4479" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">st  andrew s stadium
+  birmingham </t>
+        </is>
+      </c>
+      <c r="C4479" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4480">
+      <c r="A4480" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">loftus road
+  london </t>
+        </is>
+      </c>
+      <c r="C4480" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4481">
+      <c r="A4481" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">the den
+  london </t>
+        </is>
+      </c>
+      <c r="C4481" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4482">
+      <c r="A4482" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">coventry building society arena
+  coventry </t>
+        </is>
+      </c>
+      <c r="C4482" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4483">
+      <c r="A4483" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">envirovent stadium
+  harrogate </t>
+        </is>
+      </c>
+      <c r="C4483" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4484">
+      <c r="A4484" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ewood park
+  blackburn </t>
+        </is>
+      </c>
+      <c r="C4484" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4485">
+      <c r="A4485" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">oakwell
+  barnsley </t>
+        </is>
+      </c>
+      <c r="C4485" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4486">
+      <c r="A4486" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B4486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">riverside stadium
+  middlesbrough </t>
+        </is>
+      </c>
+      <c r="C4486" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4487">
+      <c r="A4487" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4487" t="inlineStr">
+        <is>
+          <t>dKVYSSZa</t>
+        </is>
+      </c>
+      <c r="C4487" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4488">
+      <c r="A4488" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4488" t="inlineStr">
+        <is>
+          <t>n94TZqsm</t>
+        </is>
+      </c>
+      <c r="C4488" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4489">
+      <c r="A4489" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4489" t="inlineStr">
+        <is>
+          <t>d6KwHx8i</t>
+        </is>
+      </c>
+      <c r="C4489" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4490">
+      <c r="A4490" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4490" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="C4490" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4491">
+      <c r="A4491" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4491" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="C4491" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4492">
+      <c r="A4492" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4492" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="C4492" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4493">
+      <c r="A4493" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4493" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="C4493" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4494">
+      <c r="A4494" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4494" t="inlineStr">
+        <is>
+          <t>6watkf6m</t>
+        </is>
+      </c>
+      <c r="C4494" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4495">
+      <c r="A4495" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4495" t="inlineStr">
+        <is>
+          <t>IPNnvzM7</t>
+        </is>
+      </c>
+      <c r="C4495" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4496">
+      <c r="A4496" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4496" t="inlineStr">
+        <is>
+          <t>pQTmYFAh</t>
+        </is>
+      </c>
+      <c r="C4496" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4497">
+      <c r="A4497" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4497" t="inlineStr">
+        <is>
+          <t>dtwAbyJ5</t>
+        </is>
+      </c>
+      <c r="C4497" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4498">
+      <c r="A4498" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4498" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="C4498" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="4499">
+      <c r="A4499" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4499" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="C4499" t="n">
+        <v>449</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4499"/>
+  <dimension ref="A1:C4501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61654,6 +61654,38 @@
         <v>449</v>
       </c>
     </row>
+    <row r="4500">
+      <c r="A4500" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">attwell s 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4500" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4501">
+      <c r="A4501" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">england d 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4501" t="n">
+        <v>179</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4501"/>
+  <dimension ref="A1:C4502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61686,6 +61686,21 @@
         <v>179</v>
       </c>
     </row>
+    <row r="4502">
+      <c r="A4502" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4502" t="inlineStr">
+        <is>
+          <t>QHesBmSQ</t>
+        </is>
+      </c>
+      <c r="C4502" t="n">
+        <v>451</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4502"/>
+  <dimension ref="A1:C4503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61701,6 +61701,21 @@
         <v>451</v>
       </c>
     </row>
+    <row r="4503">
+      <c r="A4503" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4503" t="inlineStr">
+        <is>
+          <t>lnG1OUjk</t>
+        </is>
+      </c>
+      <c r="C4503" t="n">
+        <v>452</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4503"/>
+  <dimension ref="A1:C4510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61716,6 +61716,116 @@
         <v>452</v>
       </c>
     </row>
+    <row r="4504">
+      <c r="A4504" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4504" t="inlineStr">
+        <is>
+          <t xml:space="preserve">howard p 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4504" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4505">
+      <c r="A4505" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4505" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4505" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4506">
+      <c r="A4506" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4506" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linington j 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4506" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4507">
+      <c r="A4507" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4507" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bankes p 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4507" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4508">
+      <c r="A4508" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smith l 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4508" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4509">
+      <c r="A4509" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4509" t="inlineStr">
+        <is>
+          <t>Uu6L6Igl</t>
+        </is>
+      </c>
+      <c r="C4509" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="4510">
+      <c r="A4510" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B4510" t="inlineStr">
+        <is>
+          <t>thRJMAq0</t>
+        </is>
+      </c>
+      <c r="C4510" t="n">
+        <v>450</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4510"/>
+  <dimension ref="A1:C4511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61826,6 +61826,21 @@
         <v>450</v>
       </c>
     </row>
+    <row r="4511">
+      <c r="A4511" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4511" t="inlineStr">
+        <is>
+          <t>MeAQUqrN</t>
+        </is>
+      </c>
+      <c r="C4511" t="n">
+        <v>454</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4511"/>
+  <dimension ref="A1:C4512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61841,6 +61841,21 @@
         <v>454</v>
       </c>
     </row>
+    <row r="4512">
+      <c r="A4512" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B4512" t="inlineStr">
+        <is>
+          <t>4fYy95jc</t>
+        </is>
+      </c>
+      <c r="C4512" t="n">
+        <v>455</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/data/england/p6_deployment/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4512"/>
+  <dimension ref="A1:C4513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61856,6 +61856,22 @@
         <v>455</v>
       </c>
     </row>
+    <row r="4513">
+      <c r="A4513" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B4513" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bramall t 
+  eng </t>
+        </is>
+      </c>
+      <c r="C4513" t="n">
+        <v>181</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
